--- a/reports/tables/Table1_Baseline_Characteristics_Final1.xlsx
+++ b/reports/tables/Table1_Baseline_Characteristics_Final1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,579 +566,714 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Baseline FSH (IU/L) (39 missing) [median (IQR)]</t>
+          <t>Male age (years) [median (IQR)]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.88 (5.80–8.25)</t>
+          <t>36.00 (33.00–40.00)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.52 (5.58–7.83)</t>
+          <t>35.00 (33.00–39.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.90 (5.80–8.31)</t>
+          <t>37.00 (33.00–40.00)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.38 (-0.73 to -0.08)</t>
+          <t>-2.00 (-2.00 to 0.00)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Initial sperm concentration (×10⁶/mL) [median (IQR)]</t>
+          <t>Baseline FSH (IU/L) (39 missing) [median (IQR)]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.31 (21.96–70.97)</t>
+          <t>6.88 (5.80–8.25)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.89 (24.95–75.94)</t>
+          <t>6.52 (5.58–7.83)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.22 (21.58–70.64)</t>
+          <t>6.90 (5.80–8.31)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+7.67 (-2.66 to 17.57)</t>
+          <t>-0.38 (-0.73 to -0.08)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prewash TPMSC (million) (1 missing) [median (IQR)]</t>
+          <t>Baseline LH (IU/L) (39 missing) [median (IQR)]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>49.11 (17.24–105.56)</t>
+          <t>5.72 (4.37–7.38)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>61.21 (19.03–128.03)</t>
+          <t>5.90 (4.42–7.59)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.26 (16.98–104.29)</t>
+          <t>5.71 (4.36–7.36)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>+12.95 (-2.90 to 32.86)</t>
+          <t>+0.20 (-0.19 to 0.54)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Prewash sperm concentration (×10⁶/mL) [median (IQR)]</t>
+          <t>Baseline E2 (pg/mL) (41 missing) [median (IQR)]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>42.60 (22.44–71.67)</t>
+          <t>36.57 (27.17–47.96)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>50.22 (29.57–78.55)</t>
+          <t>36.67 (27.90–47.80)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>42.17 (22.23–70.89)</t>
+          <t>36.57 (27.10–47.97)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+8.05 (2.22 to 14.58)</t>
+          <t>+0.10 (-2.48 to 2.54)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Postwash TPMSC (million) [median (IQR)]</t>
+          <t>Baseline prolactin (ng/mL) (38 missing) [median (IQR)]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.64 (3.68–24.25)</t>
+          <t>19.70 (14.81–26.00)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14.28 (5.11–32.82)</t>
+          <t>20.63 (15.20–26.40)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.43 (3.60–23.53)</t>
+          <t>19.66 (14.80–25.90)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>+3.85 (0.53 to 6.43)</t>
+          <t>+0.97 (-0.95 to 2.20)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Postwash sperm concentration (×10⁶/mL) [median (IQR)]</t>
+          <t>Initial sperm concentration (×10⁶/mL) [median (IQR)]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22.20 (8.02–50.27)</t>
+          <t>41.31 (21.96–70.97)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>30.31 (11.24–67.54)</t>
+          <t>48.89 (24.95–75.94)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21.80 (7.84–49.43)</t>
+          <t>41.22 (21.58–70.64)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+8.51 (0.98 to 14.28)</t>
+          <t>+7.67 (-2.66 to 17.57)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Number of mature follicles [median (IQR)]</t>
+          <t>Prewash TPMSC (million) (1 missing) [median (IQR)]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.00 (1.00–2.00)</t>
+          <t>49.11 (17.23–105.56)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.00 (1.00–2.00)</t>
+          <t>61.21 (19.03–128.03)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.00 (1.00–2.00)</t>
+          <t>48.26 (16.98–104.29)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+0.00 (0.00 to 0.00)</t>
+          <t>+12.95 (-2.90 to 32.86)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Endometrial thickness (mm) [median (IQR)]</t>
+          <t>Prewash sperm concentration (×10⁶/mL) [median (IQR)]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8.00 (6.50–9.50)</t>
+          <t>42.60 (22.44–71.67)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.70 (6.55–9.25)</t>
+          <t>50.22 (29.57–78.55)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.00 (6.40–9.50)</t>
+          <t>42.17 (22.23–70.89)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-0.30 (-0.60 to 0.00)</t>
+          <t>+8.05 (2.22 to 14.58)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IUI cycle day (2 missing) [median (IQR)]</t>
+          <t>Postwash TPMSC (million) [median (IQR)]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14.00 (14.00–15.00)</t>
+          <t>10.64 (3.68–24.25)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.00 (14.00–16.00)</t>
+          <t>14.28 (5.11–32.82)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>14.00 (14.00–15.00)</t>
+          <t>10.43 (3.60–23.53)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>+1.00 (0.00 to 1.00)</t>
+          <t>+3.85 (0.53 to 6.43)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Infertility type</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>Postwash sperm concentration (×10⁶/mL) [median (IQR)]</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>22.20 (8.02–50.27)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>30.31 (11.24–67.54)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>21.80 (7.84–49.43)</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+4.4 pp (-2.1 to 11.0)</t>
+          <t>+8.51 (0.98 to 14.28)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Primary</t>
+          <t>Number of mature follicles [median (IQR)]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2229 (75.7%)</t>
+          <t>1.00 (1.00–2.00)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>131 (71.6%)</t>
+          <t>1.00 (1.00–2.00)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2098 (76.0%)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>1.00 (1.00–2.00)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>+0.00 (0.00 to 0.00)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Secondary</t>
+          <t>Endometrial thickness (mm) [median (IQR)]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>716 (24.3%)</t>
+          <t>8.00 (6.50–9.50)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>52 (28.4%)</t>
+          <t>7.70 (6.55–9.25)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>664 (24.0%)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>8.00 (6.40–9.50)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-0.30 (-0.60 to 0.00)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Uterine factor</t>
+          <t>IUI cycle day (2 missing) [median (IQR)]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>904 (30.7%)</t>
+          <t>14.00 (14.00–15.00)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15 (8.2%)</t>
+          <t>15.00 (14.00–16.00)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>889 (32.2%)</t>
+          <t>14.00 (14.00–15.00)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-24.0 pp (-28.5 to -19.2)</t>
+          <t>+1.00 (0.00 to 1.00)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tubal factor</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>170 (5.8%)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>6 (3.3%)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>164 (5.9%)</t>
-        </is>
-      </c>
+          <t>Infertility type</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-2.7 pp (-5.3 to 0.4)</t>
+          <t>+4.4 pp (-2.1 to 11.0)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovarian factor</t>
+          <t xml:space="preserve">  Primary</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>199 (6.8%)</t>
+          <t>2229 (75.7%)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4 (2.2%)</t>
+          <t>131 (71.6%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>195 (7.1%)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-4.9 pp (-7.1 to -2.4)</t>
-        </is>
-      </c>
+          <t>2098 (76.0%)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovulatory factor (1 missing)</t>
+          <t xml:space="preserve">  Secondary</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>339 (11.5%)</t>
+          <t>716 (24.3%)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>23 (12.6%)</t>
+          <t>52 (28.4%)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>316 (11.4%)</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>+1.1 pp (-3.7 to 6.2)</t>
-        </is>
-      </c>
+          <t>664 (24.0%)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Endometriosis</t>
+          <t>Uterine factor</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>49 (1.7%)</t>
+          <t>904 (30.7%)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1 (0.5%)</t>
+          <t>15 (8.2%)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>48 (1.7%)</t>
+          <t>889 (32.2%)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-1.2 pp (-2.1 to 0.1)</t>
+          <t>-24.0 pp (-28.5 to -19.2)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Multisystem factor</t>
+          <t>Tubal factor</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>243 (8.3%)</t>
+          <t>170 (5.8%)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5 (2.7%)</t>
+          <t>6 (3.3%)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>238 (8.6%)</t>
+          <t>164 (5.9%)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-5.9 pp (-8.3 to -2.9)</t>
+          <t>-2.7 pp (-5.3 to 0.4)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gynecological surgical history (1 missing)</t>
+          <t>Ovarian factor</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>291 (9.9%)</t>
+          <t>199 (6.8%)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10 (5.5%)</t>
+          <t>4 (2.2%)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>281 (10.2%)</t>
+          <t>195 (7.1%)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-4.7 pp (-8.0 to -1.1)</t>
+          <t>-4.9 pp (-7.1 to -2.4)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IUI cycle number</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+          <t>Ovulatory factor (1 missing)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>339 (11.5%)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>23 (12.6%)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>316 (11.4%)</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>+0.03 (-0.07 to 0.14)</t>
+          <t>+1.1 pp (-3.7 to 6.2)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cycle 1</t>
+          <t>Cervical factor</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1664 (56.5%)</t>
+          <t>20 (0.7%)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>99 (54.1%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1565 (56.7%)</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>20 (0.7%)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-0.7 pp (-1.1 to -0.4)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cycle 2</t>
+          <t>Endometriosis</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>916 (31.1%)</t>
+          <t>49 (1.7%)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>60 (32.8%)</t>
+          <t>1 (0.5%)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>856 (31.0%)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>48 (1.7%)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-1.2 pp (-2.1 to 0.1)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Multisystem factor</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>243 (8.3%)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5 (2.7%)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>238 (8.6%)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-5.9 pp (-8.3 to -2.9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Gynecological surgical history (1 missing)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>291 (9.9%)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>10 (5.5%)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>281 (10.2%)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-4.7 pp (-8.0 to -1.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>IUI cycle number</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>+0.03 (-0.07 to 0.14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cycle 1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1664 (56.5%)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>99 (54.1%)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1565 (56.7%)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cycle 2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>916 (31.1%)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>60 (32.8%)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>856 (31.0%)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Cycle 3</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>365 (12.4%)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>24 (13.1%)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>341 (12.3%)</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
